--- a/data/trans_dic/P1804_2016_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1804_2016_2023-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 9,25</t>
+          <t>4,45; 9,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,39</t>
+          <t>5,99; 11,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 13,35</t>
+          <t>5,23; 13,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,52</t>
+          <t>5,86; 9,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,6</t>
+          <t>2,7; 7,06</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,91</t>
+          <t>3,21; 6,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 11,64</t>
+          <t>4,41; 12,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,92</t>
+          <t>8,02; 13,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 12,7</t>
+          <t>8,25; 14,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,27</t>
+          <t>6,2; 9,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 11,16</t>
+          <t>7,08; 12,04</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,73</t>
+          <t>2,44; 5,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,29</t>
+          <t>3,08; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,34</t>
+          <t>6,79; 11,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 9,95</t>
+          <t>6,28; 9,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,01</t>
+          <t>5,22; 7,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,82</t>
+          <t>5,07; 7,91</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,27</t>
+          <t>3,69; 7,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,4</t>
+          <t>5,0; 9,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,35</t>
+          <t>4,58; 8,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,16</t>
+          <t>6,01; 9,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,22</t>
+          <t>4,58; 7,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,22</t>
+          <t>6,05; 8,76</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,89</t>
+          <t>5,52; 10,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,33</t>
+          <t>5,35; 9,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 13,98</t>
+          <t>8,15; 13,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,88</t>
+          <t>6,86; 10,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 11,95</t>
+          <t>7,68; 11,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,02</t>
+          <t>6,61; 9,16</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 14,85</t>
+          <t>8,12; 15,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,86</t>
+          <t>6,27; 10,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,39; 15,25</t>
+          <t>8,69; 15,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,71</t>
+          <t>6,55; 10,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 14,14</t>
+          <t>9,05; 14,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,88</t>
+          <t>6,96; 9,78</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 13,0</t>
+          <t>6,16; 12,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,66</t>
+          <t>5,0; 9,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 20,8</t>
+          <t>11,71; 20,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,8</t>
+          <t>6,92; 10,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,47; 16,66</t>
+          <t>10,24; 16,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,58</t>
+          <t>6,59; 9,65</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,26</t>
+          <t>5,44; 7,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,56</t>
+          <t>5,35; 7,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,09; 11,05</t>
+          <t>8,83; 10,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,63</t>
+          <t>7,67; 9,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,86</t>
+          <t>7,43; 8,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,3</t>
+          <t>6,76; 8,05</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>34668</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17732; 38781</t>
+          <t>18686; 39475</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 16214</t>
+          <t>0; 24824</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24278; 45067</t>
+          <t>23710; 46697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15124; 41483</t>
+          <t>18726; 48271</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>47597; 77595</t>
+          <t>47806; 77932</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15910; 46884</t>
+          <t>20666; 54062</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>36885</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47316</t>
+          <t>55478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77481</t>
+          <t>92363</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19031; 40823</t>
+          <t>18955; 39251</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18082; 49309</t>
+          <t>21020; 60165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45920; 72784</t>
+          <t>45185; 73511</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27478; 64920</t>
+          <t>41244; 72335</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71026; 106959</t>
+          <t>71540; 106562</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56564; 104310</t>
+          <t>69143; 117622</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>49667</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67743</t>
+          <t>78927</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17030; 38361</t>
+          <t>16303; 36717</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16174; 39124</t>
+          <t>19152; 42897</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45440; 74986</t>
+          <t>44898; 74883</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33825; 53999</t>
+          <t>39091; 60716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68601; 106574</t>
+          <t>69430; 106033</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53893; 84316</t>
+          <t>63070; 98350</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47917</t>
+          <t>54501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89816</t>
+          <t>103780</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22540; 46938</t>
+          <t>23815; 48117</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18663; 65671</t>
+          <t>35022; 69050</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30112; 54171</t>
+          <t>29723; 54569</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36427; 58205</t>
+          <t>44292; 68403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57613; 93497</t>
+          <t>59380; 92028</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54288; 115604</t>
+          <t>86956; 125863</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38970</t>
+          <t>43862</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44157</t>
+          <t>51359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83127</t>
+          <t>95220</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26993; 52033</t>
+          <t>26386; 51585</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28820; 52340</t>
+          <t>32580; 57944</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40215; 69438</t>
+          <t>40484; 69173</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35599; 54007</t>
+          <t>41688; 62857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>75131; 116505</t>
+          <t>74889; 113630</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69816; 99987</t>
+          <t>80473; 111451</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63623</t>
+          <t>69395</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26621; 49632</t>
+          <t>27131; 51296</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22705; 39986</t>
+          <t>25504; 43326</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31709; 57610</t>
+          <t>32835; 59016</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12487; 53008</t>
+          <t>28755; 44478</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65233; 100680</t>
+          <t>64441; 99707</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33140; 86735</t>
+          <t>58881; 82772</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>40453</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56802</t>
+          <t>62046</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16485; 33412</t>
+          <t>15844; 32836</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14054; 27302</t>
+          <t>15518; 29619</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47382; 83217</t>
+          <t>46859; 80916</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29214; 45922</t>
+          <t>32116; 50520</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68822; 109476</t>
+          <t>67298; 106846</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46399; 67812</t>
+          <t>51018; 74746</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>276729</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>467563</t>
+          <t>536400</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>186939; 246481</t>
+          <t>184751; 243225</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>152011; 226927</t>
+          <t>189032; 258774</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>322187; 391829</t>
+          <t>312856; 388852</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>228617; 315698</t>
+          <t>286074; 351492</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>520169; 614524</t>
+          <t>515476; 615517</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>403907; 519745</t>
+          <t>491092; 584145</t>
         </is>
       </c>
     </row>
